--- a/docs/TripPlanner_TestSchedule.xlsx
+++ b/docs/TripPlanner_TestSchedule.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Schedule" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,26 +72,8 @@
       <color rgb="00843C0C"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="25">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -207,38 +188,8 @@
         <bgColor rgb="00FBE9E7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F7"/>
-        <bgColor rgb="00D6E4F7"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -260,55 +211,11 @@
         <color rgb="00BDD7EE"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BDD7EE"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BDD7EE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BDD7EE"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BDD7EE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BDD7EE"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BDD7EE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BDD7EE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BDD7EE"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -410,53 +317,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -824,32 +684,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trip Planner QA – Test Schedule   |   Cairo → Marsa Alam</t>
+          <t>Trip Planner QA  -  Test Schedule  -  Cairo to Marsa Alam</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scenario: User searches flights, checks weather, looks up restaurants near Marsa Alam and sorts by rating</t>
+          <t>User searches for flights, checks weather, finds restaurants near Marsa Alam and sorts by rating</t>
         </is>
       </c>
     </row>
@@ -871,35 +730,30 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Test Description</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Test Objective</t>
+          <t>Test Steps</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Test Steps</t>
+          <t>Expected Result</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Expected Result</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -912,7 +766,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5" ht="50" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -926,39 +780,34 @@
           <t>Google Flights UI</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Smoke</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>The flights page loads and the search form is visible</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Page loads correctly</t>
+          <t>Open google.com/travel/flights</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Open https://www.google.com/travel/flights</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Page title says Flights and the search form is visible</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
+          <t>Page title says Flights and the search form is there</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="50" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -972,39 +821,34 @@
           <t>Google Flights UI</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>The origin field accepts Cairo and shows airport suggestions</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Origin field accepts Cairo</t>
+          <t>Click the origin field and type Cairo, then look at the dropdown</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Click the origin field and type Cairo — check the autocomplete dropdown</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>Cairo International Airport (CAI) appears as a suggestion</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="inlineStr"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
+          <t>Cairo International Airport CAI appears as a selectable option</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr"/>
+    </row>
+    <row r="7" ht="50" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
@@ -1018,39 +862,34 @@
           <t>Google Flights UI</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>The destination field accepts Marsa Alam and shows the right airport</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Destination field accepts Marsa Alam</t>
+          <t>After setting Cairo as origin, click destination and type Marsa Alam</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>After setting Cairo as origin, click destination and type Marsa Alam</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Marsa Alam (RMF) shows up in the suggestions</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
+          <t>Marsa Alam RMF shows up in the suggestions list</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -1064,43 +903,38 @@
           <t>Google Flights UI</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Searching Cairo to Marsa Alam brings back at least one flight</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Search returns at least one flight result</t>
+          <t>Set origin to Cairo, destination to Marsa Alam, then click Search</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Set origin = Cairo, destination = Marsa Alam, click Search</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>At least one flight card appears. Search should not come back empty</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
+          <t>At least one flight card appears on the results page. Search should not come back empty</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>Core happy path</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
@@ -1114,39 +948,34 @@
           <t>Google Flights UI</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>The results page header confirms the correct route was searched</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Results page confirms the correct route</t>
+          <t>After the search completes, check the page header or title text</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>After search, check the page header or title text</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Both cities appear somewhere — full names or airport codes CAI and RMF</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+          <t>Both cities are mentioned somewhere, either full names or the airport codes CAI and RMF</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -1160,39 +989,34 @@
           <t>Google Flights UI</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>The first result card shows the airline name</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>First result card shows an airline name</t>
+          <t>Look at the first result card on the results page</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Look at the first result card on the results page</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
           <t>Airline name is visible and not blank or cut off</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="inlineStr"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr"/>
+    </row>
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
@@ -1206,39 +1030,34 @@
           <t>Google Flights UI</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>The first result card shows a price</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>First result card shows a price</t>
+          <t>Check the price field on the first result card</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Check the price field on the first result card</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>A price is shown. Not N/A, not empty — any currency is fine</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="48" customHeight="1">
+          <t>A price is shown. Not empty, any currency is fine</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -1252,37 +1071,32 @@
           <t>Google Flights UI</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>No no-results error message appears after a valid search</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>No-results error banner does not appear</t>
+          <t>After submitting the Cairo to Marsa Alam search, scan the page for any error banner</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>After submitting Cairo → Marsa Alam search, scan page for any no-results message</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>No 'no flights found' banner. If it shows, route or data has a problem</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr"/>
+          <t>No no-flights-found message is displayed. If it shows up, the route or data has a problem</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
@@ -1291,7 +1105,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="15" t="n">
         <v>9</v>
       </c>
@@ -1305,39 +1119,34 @@
           <t>Google Search - Weather</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Smoke</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Searching Marsa Alam weather loads a results page</t>
+        </is>
+      </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Weather search loads a results page</t>
+          <t>Go to google.com, type Marsa Alam weather in the search box and press Enter</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>Go to google.com, type 'Marsa Alam weather', hit Enter</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>Results page loads and URL reflects the query</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
+          <t>Results page loads and the URL reflects the query</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr"/>
+    </row>
+    <row r="15" ht="50" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>10</v>
       </c>
@@ -1351,43 +1160,38 @@
           <t>Google Search - Weather</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>The Google weather card is visible on the results page</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Google weather widget is visible on the SERP</t>
+          <t>After the weather search, look for the weather card that usually appears at the top of results</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>After the weather search, look for the weather card at the top of results</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>The card is visible — shows temperature, condition, and location</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>Widget can take 2-3 seconds to render</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
+          <t>The card is visible and shows temperature, condition, and location</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>Can take 2-3 seconds to render</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="15" t="n">
         <v>11</v>
       </c>
@@ -1401,43 +1205,38 @@
           <t>Google Search - Weather</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>The weather widget location label says Marsa Alam</t>
+        </is>
+      </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>Widget location label shows Marsa Alam</t>
+          <t>Check the location label inside the weather widget</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>Check the location label inside the weather widget</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>It says Marsa Alam — not Cairo or any other city</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
+          <t>It says Marsa Alam, not Cairo or any other city. Wrong city here makes the whole result misleading</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>Key relevance check</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1">
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="10" t="n">
         <v>12</v>
       </c>
@@ -1451,39 +1250,34 @@
           <t>Google Search - Weather</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>The weather card shows a temperature number</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Widget shows a temperature number</t>
+          <t>Read the temperature from the weather card</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Read the temperature from the weather card</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
           <t>An actual number is there, not a dash or empty space</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr"/>
-    </row>
-    <row r="18" ht="48" customHeight="1">
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="15" t="n">
         <v>13</v>
       </c>
@@ -1497,39 +1291,34 @@
           <t>Google Search - Weather</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>The weather card shows a condition description</t>
+        </is>
+      </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>Widget shows a weather condition text</t>
+          <t>Check the condition text in the card, usually something like Sunny or Partly cloudy</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>Check the condition text in the card (e.g. Sunny, Partly cloudy)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>Some condition text is visible — exact value doesn't matter as weather changes</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="48" customHeight="1">
+          <t>Some condition text is visible. Exact value does not matter since weather changes</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr"/>
+    </row>
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="10" t="n">
         <v>14</v>
       </c>
@@ -1543,39 +1332,34 @@
           <t>Google Search - Weather</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>The temperature shown is a realistic value for Marsa Alam</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Temperature is within a realistic range for Marsa Alam</t>
+          <t>Parse the temperature number from the widget</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Parse the temperature number from the widget and check it</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Between 5°C and 55°C. Marsa Alam is Red Sea coast — never freezes, record high ~48°C</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>Outside this range = likely wrong data</t>
+          <t>Between 5 and 55 Celsius. Marsa Alam is on the Red Sea coast and never freezes. Record high is around 48</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>Outside this range means something is wrong with the data</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1370,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1">
+    <row r="21" ht="50" customHeight="1">
       <c r="A21" s="19" t="n">
         <v>15</v>
       </c>
@@ -1600,39 +1384,34 @@
           <t>Google Search - Restaurants</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Smoke</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Searching restaurant near Marsa Alam loads a results page</t>
+        </is>
+      </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>Restaurant search loads a results page</t>
+          <t>Go to google.com and search for restaurant near Marsa Alam</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>Go to google.com, search for 'restaurant near Marsa Alam'</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>Results page loads. Basic check that the search goes through</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22" ht="48" customHeight="1">
+          <t>Results page loads. Basic check that the search goes through without errors</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="50" customHeight="1">
       <c r="A22" s="10" t="n">
         <v>16</v>
       </c>
@@ -1646,39 +1425,34 @@
           <t>Google Search - Restaurants</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>At least one restaurant card appears in the local panel</t>
+        </is>
+      </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>At least one restaurant card appears</t>
+          <t>Look for the local restaurant cards in the map pack area of the results page</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Look for local restaurant cards in the map pack / local panel</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>At least one card is there. Empty panel = locator issue or no results returned</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23" ht="48" customHeight="1">
+          <t>At least one card is there. Completely empty panel means either no results or a locator issue</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23" ht="50" customHeight="1">
       <c r="A23" s="19" t="n">
         <v>17</v>
       </c>
@@ -1692,39 +1466,34 @@
           <t>Google Search - Restaurants</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>A sort control is visible above the restaurant results</t>
+        </is>
+      </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>Sort control is visible above restaurant results</t>
+          <t>Check if a sort or filter button is visible above the restaurant cards</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Check if a sort or filter button is present above the cards</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>Some sort control is visible (Relevance / Distance / Highest rated options)</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J23" s="21" t="inlineStr"/>
-    </row>
-    <row r="24" ht="48" customHeight="1">
+          <t>Some sort control is there. Google usually shows Relevance, Distance, Highest rated options</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="10" t="n">
         <v>18</v>
       </c>
@@ -1738,39 +1507,34 @@
           <t>Google Search - Restaurants</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Selecting Highest rated updates the list without breaking the page</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Selecting Highest Rated updates the list</t>
+          <t>Click the sort button and select Highest rated</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Click the sort button and select Highest rated</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>Page updates and still shows restaurants. Shouldn't crash or go blank</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr"/>
-    </row>
-    <row r="25" ht="48" customHeight="1">
+          <t>Page updates and restaurants are still shown. Should not crash or go blank</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25" ht="50" customHeight="1">
       <c r="A25" s="19" t="n">
         <v>19</v>
       </c>
@@ -1784,43 +1548,38 @@
           <t>Google Search - Restaurants</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Sorting</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>After sorting by highest rated the cards are in descending rating order</t>
+        </is>
+      </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>Cards are sorted highest rating first</t>
+          <t>Compare the rating of the first card with the rating of the last visible card</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>After sorting, compare rating of first card vs last visible card</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>First card rating &gt;= last card rating. If reversed, sort is broken</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>Core sort verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1">
+          <t>First card rating is equal to or higher than the last card. If reversed the sort is not working</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>Core sort check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="50" customHeight="1">
       <c r="A26" s="10" t="n">
         <v>20</v>
       </c>
@@ -1834,37 +1593,32 @@
           <t>Google Search - Restaurants</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>All visible restaurant cards have text content</t>
+        </is>
+      </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>All visible restaurant cards have text content</t>
+          <t>Go through each visible card and check that text is actually there</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Go through each visible card and check for text</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>Every card has a name or some visible content — empty card = rendering bug</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J26" s="12" t="inlineStr"/>
+          <t>Every card has a name or some visible content. An empty card would be a rendering bug</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr"/>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="22" t="inlineStr">
@@ -1873,7 +1627,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
+    <row r="28" ht="50" customHeight="1">
       <c r="A28" s="23" t="n">
         <v>21</v>
       </c>
@@ -1887,43 +1641,38 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Auth</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>The token endpoint hands back a valid access token</t>
+        </is>
+      </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>Token endpoint returns access token</t>
+          <t>POST to the token endpoint with valid client_id and client_secret credentials</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>POST to token endpoint with valid client_id and client_secret</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="inlineStr">
-        <is>
-          <t>HTTP 200 with access_token in response. Without this none of the other Amadeus tests run</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J28" s="25" t="inlineStr">
-        <is>
-          <t>Run first, token reused by other tests</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="48" customHeight="1">
+          <t>HTTP 200 with access_token in the response body. Without this the other Amadeus tests cannot run</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I28" s="25" t="inlineStr">
+        <is>
+          <t>Run this first, token is reused by other tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="50" customHeight="1">
       <c r="A29" s="10" t="n">
         <v>22</v>
       </c>
@@ -1937,43 +1686,38 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>The flight offers endpoint responds with HTTP 200 for the CAI to RMF route</t>
+        </is>
+      </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Flight offers endpoint returns HTTP 200</t>
+          <t>GET /shopping/flight-offers with originLocationCode=CAI, destinationLocationCode=RMF, departure date 30 days out, 1 adult</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>GET /shopping/flight-offers with originLocationCode=CAI, destinationLocationCode=RMF, date +30 days, 1 adult</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>HTTP 200. 400 or 401 means problem with request or token</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>Mock: http://localhost:9083</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="48" customHeight="1">
+          <t>HTTP 200. A 400 or 401 back means something is wrong with the request or the token</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Mock: localhost:9083</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="50" customHeight="1">
       <c r="A30" s="23" t="n">
         <v>23</v>
       </c>
@@ -1987,39 +1731,34 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>The response data array contains at least one flight offer</t>
+        </is>
+      </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>Response data array has at least one offer</t>
+          <t>Parse the response body and check the length of the data array</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>Parse response body and check data array length</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="inlineStr">
-        <is>
-          <t>data array exists and has at least one item. Empty array = no flights found</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J30" s="25" t="inlineStr"/>
-    </row>
-    <row r="31" ht="48" customHeight="1">
+          <t>data array has at least one item. Empty array for this route would be unexpected</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I30" s="25" t="inlineStr"/>
+    </row>
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="10" t="n">
         <v>24</v>
       </c>
@@ -2033,39 +1772,34 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Every offer in the data array has an id field</t>
+        </is>
+      </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Every offer in data array has an id</t>
+          <t>Loop through all offers and check each one has an id</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Loop through all offers and check each has an id field</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>No offer is missing its id. If one is null the response structure is broken</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="inlineStr"/>
-    </row>
-    <row r="32" ht="48" customHeight="1">
+          <t>No offer is missing its id. A null id means the response structure is broken</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32" ht="50" customHeight="1">
       <c r="A32" s="23" t="n">
         <v>25</v>
       </c>
@@ -2079,39 +1813,34 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>The first segment departure IATA code matches the searched origin</t>
+        </is>
+      </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>First segment departure IATA code is CAI</t>
+          <t>Read data[0].itineraries[0].segments[0].departure.iataCode</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>Check data[0].itineraries[0].segments[0].departure.iataCode</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="inlineStr">
-        <is>
-          <t>Value is CAI. Anything else means origin filtering is not working</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J32" s="25" t="inlineStr"/>
-    </row>
-    <row r="33" ht="48" customHeight="1">
+          <t>Value is CAI. Anything else means the origin filtering is not working correctly</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I32" s="25" t="inlineStr"/>
+    </row>
+    <row r="33" ht="50" customHeight="1">
       <c r="A33" s="10" t="n">
         <v>26</v>
       </c>
@@ -2125,39 +1854,34 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>The last segment arrival IATA code matches the searched destination</t>
+        </is>
+      </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Last segment arrival IATA code is RMF</t>
+          <t>Check the last segment of the first itinerary, whether it is a direct flight or a connection</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Check last segment of first itinerary — could be direct or last leg of connection</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>arrival.iataCode is RMF. Destination must match what was searched</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J33" s="12" t="inlineStr"/>
-    </row>
-    <row r="34" ht="48" customHeight="1">
+          <t>arrival.iataCode is RMF. Destination must match what was actually searched</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34" ht="50" customHeight="1">
       <c r="A34" s="23" t="n">
         <v>27</v>
       </c>
@@ -2171,39 +1895,34 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>Each flight offer has a price with a total value</t>
+        </is>
+      </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>Price object has a total field</t>
+          <t>Check the price object on the first offer</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>Check the price object on the first offer</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="inlineStr">
-        <is>
-          <t>price.total is present and has a value. Offer without price is useless</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J34" s="25" t="inlineStr"/>
-    </row>
-    <row r="35" ht="48" customHeight="1">
+          <t>price.total is present and not empty. An offer with no price is not useful</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I34" s="25" t="inlineStr"/>
+    </row>
+    <row r="35" ht="50" customHeight="1">
       <c r="A35" s="10" t="n">
         <v>28</v>
       </c>
@@ -2217,39 +1936,34 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>The price.total value is a valid number</t>
+        </is>
+      </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>price.total parses as a valid number</t>
+          <t>Take the price.total string and try parsing it as a decimal number</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Take the price.total string and try to parse it as a decimal</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>Parses without errors. Amadeus returns prices like '450.00' — bad chars = data issue</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="inlineStr"/>
-    </row>
-    <row r="36" ht="48" customHeight="1">
+          <t>Parses cleanly. Amadeus returns prices like 450.00 as strings. Unexpected characters would mean a data issue</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36" ht="50" customHeight="1">
       <c r="A36" s="23" t="n">
         <v>29</v>
       </c>
@@ -2263,39 +1977,34 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>The flight offers endpoint responds within 5 seconds</t>
+        </is>
+      </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>Response time under 5 seconds</t>
+          <t>Measure the time from sending the request to receiving the full response</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>Measure time from sending request to receiving full response</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="inlineStr">
-        <is>
-          <t>Under 5 seconds. Amadeus test env can be slow but &gt; 5s would be a problem in prod</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J36" s="25" t="inlineStr"/>
-    </row>
-    <row r="37" ht="48" customHeight="1">
+          <t>Under 5 seconds. The Amadeus test environment can be slow but anything beyond 5s would be a problem</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I36" s="25" t="inlineStr"/>
+    </row>
+    <row r="37" ht="50" customHeight="1">
       <c r="A37" s="10" t="n">
         <v>30</v>
       </c>
@@ -2309,37 +2018,32 @@
           <t>Amadeus API - Flights</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="E37" s="26" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>P3 - Medium</t>
         </is>
       </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>The response body includes the dictionaries section</t>
+        </is>
+      </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>Response includes dictionaries section</t>
+          <t>Check for the top-level dictionaries object in the response</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Check for top-level dictionaries object in the response</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>dictionaries is present. Contains carrier names, aircraft types etc.</t>
-        </is>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="inlineStr"/>
+          <t>dictionaries is present. It holds carrier names, aircraft types and other reference data</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="27" t="inlineStr">
@@ -2348,7 +2052,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="48" customHeight="1">
+    <row r="39" ht="50" customHeight="1">
       <c r="A39" s="28" t="n">
         <v>31</v>
       </c>
@@ -2362,43 +2066,38 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D39" s="28" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E39" s="30" t="inlineStr">
+        <is>
+          <t>A valid weather request for Marsa Alam returns HTTP 200</t>
+        </is>
+      </c>
       <c r="F39" s="30" t="inlineStr">
         <is>
-          <t>Valid request returns HTTP 200</t>
+          <t>GET /weather with q=Marsa Alam,EG and units=metric and a valid API key</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
         <is>
-          <t>GET /weather with q=Marsa Alam,EG, units=metric, and valid API key</t>
-        </is>
-      </c>
-      <c r="H39" s="30" t="inlineStr">
-        <is>
           <t>HTTP 200</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J39" s="30" t="inlineStr">
-        <is>
-          <t>Mock: http://localhost:9081</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="48" customHeight="1">
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I39" s="30" t="inlineStr">
+        <is>
+          <t>Mock: localhost:9081</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="50" customHeight="1">
       <c r="A40" s="10" t="n">
         <v>32</v>
       </c>
@@ -2412,39 +2111,34 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>The name field in the response references Marsa Alam</t>
+        </is>
+      </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>name field references Marsa Alam</t>
+          <t>Read the name field from the response body</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Check the name field in the response body</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>Contains 'Marsa' somewhere. OWM sometimes varies the exact name string</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr"/>
-    </row>
-    <row r="41" ht="48" customHeight="1">
+          <t>Contains Marsa somewhere. OWM can vary the exact name string slightly</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41" ht="50" customHeight="1">
       <c r="A41" s="28" t="n">
         <v>33</v>
       </c>
@@ -2458,39 +2152,34 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D41" s="28" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E41" s="30" t="inlineStr">
+        <is>
+          <t>The main.temp field is present and is a number</t>
+        </is>
+      </c>
       <c r="F41" s="30" t="inlineStr">
         <is>
-          <t>main.temp is present and numeric</t>
+          <t>Check main.temp in the response</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
         <is>
-          <t>Check main.temp in the response</t>
-        </is>
-      </c>
-      <c r="H41" s="30" t="inlineStr">
-        <is>
-          <t>Field exists and is a number. Missing entirely = malformed response</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J41" s="30" t="inlineStr"/>
-    </row>
-    <row r="42" ht="48" customHeight="1">
+          <t>Field exists and is numeric. If it is missing entirely the response is malformed</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I41" s="30" t="inlineStr"/>
+    </row>
+    <row r="42" ht="50" customHeight="1">
       <c r="A42" s="10" t="n">
         <v>34</v>
       </c>
@@ -2504,39 +2193,34 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>The temperature value is a realistic number for Marsa Alam</t>
+        </is>
+      </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Temperature value is realistic for Marsa Alam</t>
+          <t>Check the actual value of main.temp</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Check the actual value of main.temp</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>Between 5 and 55 Celsius. Marsa Alam never freezes, record high ~48°C</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J42" s="12" t="inlineStr"/>
-    </row>
-    <row r="43" ht="48" customHeight="1">
+          <t>Between 5 and 55 Celsius. Marsa Alam never freezes and record highs are around 48</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43" ht="50" customHeight="1">
       <c r="A43" s="28" t="n">
         <v>35</v>
       </c>
@@ -2550,39 +2234,34 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D43" s="28" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E43" s="30" t="inlineStr">
+        <is>
+          <t>The weather description field has some text in it</t>
+        </is>
+      </c>
       <c r="F43" s="30" t="inlineStr">
         <is>
-          <t>weather[0].description is not blank</t>
+          <t>Check weather[0].description</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
         <is>
-          <t>Check weather[0].description field</t>
-        </is>
-      </c>
-      <c r="H43" s="30" t="inlineStr">
-        <is>
-          <t>Some text is there — 'clear sky', 'few clouds', etc. Blank = empty weather array</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J43" s="30" t="inlineStr"/>
-    </row>
-    <row r="44" ht="48" customHeight="1">
+          <t>Some text is there like clear sky or few clouds. Blank means the weather array is empty</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I43" s="30" t="inlineStr"/>
+    </row>
+    <row r="44" ht="50" customHeight="1">
       <c r="A44" s="10" t="n">
         <v>36</v>
       </c>
@@ -2596,43 +2275,38 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>The coordinates in the response match the Marsa Alam area</t>
+        </is>
+      </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>Coordinates match Marsa Alam location</t>
+          <t>Check coord.lat and coord.lon</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Check coord.lat and coord.lon in the response</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>lat ~24-26°N and lon ~33-37°E. Wildly off = OWM matched wrong city</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>Marsa Alam is at 25.07N, 34.89E</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="48" customHeight="1">
+          <t>lat is roughly 24 to 26 north and lon is roughly 33 to 37 east. Wildly off means OWM matched the wrong city</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>Marsa Alam is at 25.07N 34.89E</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="50" customHeight="1">
       <c r="A45" s="28" t="n">
         <v>37</v>
       </c>
@@ -2646,39 +2320,34 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D45" s="28" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E45" s="26" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>P3 - Medium</t>
         </is>
       </c>
+      <c r="E45" s="30" t="inlineStr">
+        <is>
+          <t>The wind speed value is zero or higher</t>
+        </is>
+      </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>wind.speed is non-negative</t>
+          <t>Check wind.speed in the response</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>Check wind.speed field</t>
-        </is>
-      </c>
-      <c r="H45" s="30" t="inlineStr">
-        <is>
-          <t>Zero or higher. Negative wind speed makes no physical sense</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J45" s="30" t="inlineStr"/>
-    </row>
-    <row r="46" ht="48" customHeight="1">
+          <t>Zero or a positive number. Negative wind speed makes no physical sense</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I45" s="30" t="inlineStr"/>
+    </row>
+    <row r="46" ht="50" customHeight="1">
       <c r="A46" s="10" t="n">
         <v>38</v>
       </c>
@@ -2692,39 +2361,34 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>The weather endpoint responds within 3 seconds</t>
+        </is>
+      </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Response time under 3 seconds</t>
+          <t>Time the full request and response cycle</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Time the full request-response cycle</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
           <t>Under 3 seconds. Weather APIs should be fast</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J46" s="12" t="inlineStr"/>
-    </row>
-    <row r="47" ht="48" customHeight="1">
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47" ht="50" customHeight="1">
       <c r="A47" s="28" t="n">
         <v>39</v>
       </c>
@@ -2738,39 +2402,34 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D47" s="28" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E47" s="30" t="inlineStr">
+        <is>
+          <t>Sending a wrong API key gets a 401 back</t>
+        </is>
+      </c>
       <c r="F47" s="30" t="inlineStr">
         <is>
-          <t>Invalid API key returns 401</t>
+          <t>Send the same request but with a fake or invalid API key</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
         <is>
-          <t>Send same request but with a fake/wrong API key</t>
-        </is>
-      </c>
-      <c r="H47" s="30" t="inlineStr">
-        <is>
-          <t>HTTP 401. API should reject invalid keys, not return data</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J47" s="30" t="inlineStr"/>
-    </row>
-    <row r="48" ht="48" customHeight="1">
+          <t>HTTP 401. The API should reject invalid keys and not return any weather data</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I47" s="30" t="inlineStr"/>
+    </row>
+    <row r="48" ht="50" customHeight="1">
       <c r="A48" s="10" t="n">
         <v>40</v>
       </c>
@@ -2784,37 +2443,32 @@
           <t>OpenWeatherMap API</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>A city name that does not exist gets a 404 back</t>
+        </is>
+      </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Non-existent city returns 404</t>
+          <t>Send a request with a city name that definitely does not exist</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Send request with a city name that definitely doesn't exist</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>HTTP 404. OWM returning 200 for a made-up city would be a problem</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J48" s="12" t="inlineStr"/>
+          <t>HTTP 404. Getting a 200 with made-up data for a nonexistent city would be a problem</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr"/>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="31" t="inlineStr">
@@ -2823,7 +2477,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="48" customHeight="1">
+    <row r="50" ht="50" customHeight="1">
       <c r="A50" s="32" t="n">
         <v>41</v>
       </c>
@@ -2837,43 +2491,38 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D50" s="32" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E50" s="34" t="inlineStr">
+        <is>
+          <t>The text search endpoint returns HTTP 200 for restaurant near Marsa Alam</t>
+        </is>
+      </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>Text search returns HTTP 200</t>
+          <t>POST to /places:searchText with textQuery set to restaurant near Marsa Alam and a valid X-Goog-Api-Key header</t>
         </is>
       </c>
       <c r="G50" s="34" t="inlineStr">
         <is>
-          <t>POST to /places:searchText with textQuery='restaurant near Marsa Alam' and valid X-Goog-Api-Key header</t>
-        </is>
-      </c>
-      <c r="H50" s="34" t="inlineStr">
-        <is>
           <t>HTTP 200</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J50" s="34" t="inlineStr">
-        <is>
-          <t>Mock: http://localhost:9082</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="48" customHeight="1">
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I50" s="34" t="inlineStr">
+        <is>
+          <t>Mock: localhost:9082</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="50" customHeight="1">
       <c r="A51" s="10" t="n">
         <v>42</v>
       </c>
@@ -2887,43 +2536,38 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>The response body has a places array and no error object</t>
+        </is>
+      </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>Response has places array and no error object</t>
+          <t>Check the response body structure. The new Places API does not have a status field like the old one</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Check response body — new Places API has no status field like old one</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>No error object in body, and places[] array is present</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>New API changed the response structure vs legacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="48" customHeight="1">
+          <t>No error object in the body and the places array is present</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>New API changed structure vs legacy endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="50" customHeight="1">
       <c r="A52" s="32" t="n">
         <v>43</v>
       </c>
@@ -2937,39 +2581,34 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D52" s="32" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E52" s="34" t="inlineStr">
+        <is>
+          <t>The places array has at least one restaurant in it</t>
+        </is>
+      </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>At least one restaurant in results</t>
+          <t>Check the length of the places array in the response</t>
         </is>
       </c>
       <c r="G52" s="34" t="inlineStr">
         <is>
-          <t>Check length of places array</t>
-        </is>
-      </c>
-      <c r="H52" s="34" t="inlineStr">
-        <is>
-          <t>At least one result. Marsa Alam has restaurants — empty = query not working</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J52" s="34" t="inlineStr"/>
-    </row>
-    <row r="53" ht="48" customHeight="1">
+          <t>At least one result. Marsa Alam has restaurants so an empty array means the query is not working</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I52" s="34" t="inlineStr"/>
+    </row>
+    <row r="53" ht="50" customHeight="1">
       <c r="A53" s="10" t="n">
         <v>44</v>
       </c>
@@ -2983,43 +2622,38 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Every place in the response has a display name</t>
+        </is>
+      </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>Every place has a displayName.text</t>
+          <t>Loop through the places array and check displayName.text on each one</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Loop through places[] and check displayName.text on each</t>
-        </is>
-      </c>
-      <c r="H53" s="12" t="inlineStr">
-        <is>
-          <t>Every place has a name. Missing = data integrity issue</t>
-        </is>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J53" s="12" t="inlineStr">
-        <is>
-          <t>New API: was 'name', now 'displayName.text'</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="48" customHeight="1">
+          <t>Every place has a name. A restaurant with no name in the response is a data integrity issue</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>New API uses displayName.text, old one used name</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="50" customHeight="1">
       <c r="A54" s="32" t="n">
         <v>45</v>
       </c>
@@ -3033,43 +2667,38 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D54" s="32" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E54" s="34" t="inlineStr">
+        <is>
+          <t>Every place has latitude and longitude coordinates</t>
+        </is>
+      </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>Every place has location.latitude and longitude</t>
+          <t>Check location.latitude and location.longitude on each result</t>
         </is>
       </c>
       <c r="G54" s="34" t="inlineStr">
         <is>
-          <t>Check location.latitude and location.longitude on each result</t>
-        </is>
-      </c>
-      <c r="H54" s="34" t="inlineStr">
-        <is>
-          <t>Both fields present for every result</t>
-        </is>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J54" s="34" t="inlineStr">
-        <is>
-          <t>New API: was 'geometry.location', now just 'location'</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="48" customHeight="1">
+          <t>Both fields are present for every result</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I54" s="34" t="inlineStr">
+        <is>
+          <t>New API uses location.latitude, old one used geometry.location.lat</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="50" customHeight="1">
       <c r="A55" s="10" t="n">
         <v>46</v>
       </c>
@@ -3083,39 +2712,34 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>The coordinates are actually within the Marsa Alam area</t>
+        </is>
+      </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>Coordinates are within Marsa Alam region</t>
+          <t>Check the lat and lng values for each result</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Check actual lat/lng values for each result</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>lat between 23-27, lng between 33-37. Totally off = matched wrong location</t>
-        </is>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J55" s="12" t="inlineStr"/>
-    </row>
-    <row r="56" ht="48" customHeight="1">
+          <t>lat is between 23 and 27, lng is between 33 and 37. Way off means the query matched the wrong location</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56" ht="50" customHeight="1">
       <c r="A56" s="32" t="n">
         <v>47</v>
       </c>
@@ -3129,39 +2753,34 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D56" s="32" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E56" s="34" t="inlineStr">
+        <is>
+          <t>Every place has a place id</t>
+        </is>
+      </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>Every place has an id (place_id)</t>
+          <t>Check the id field on each result</t>
         </is>
       </c>
       <c r="G56" s="34" t="inlineStr">
         <is>
-          <t>Check id field on each result</t>
-        </is>
-      </c>
-      <c r="H56" s="34" t="inlineStr">
-        <is>
-          <t>Every result has a place id — needed for any follow-up API calls</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J56" s="34" t="inlineStr"/>
-    </row>
-    <row r="57" ht="48" customHeight="1">
+          <t>Every result has an id. It is needed for any follow-up API calls</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I56" s="34" t="inlineStr"/>
+    </row>
+    <row r="57" ht="50" customHeight="1">
       <c r="A57" s="10" t="n">
         <v>48</v>
       </c>
@@ -3175,43 +2794,38 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Rating values are within the valid 1 to 5 range</t>
+        </is>
+      </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>Ratings are between 1.0 and 5.0</t>
+          <t>For results that have a rating field, check the value</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>For results that have a rating field, check the value</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>Between 1.0 and 5.0. Outside this range = corrupted data</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J57" s="12" t="inlineStr">
-        <is>
-          <t>Rating is optional — only check when field exists</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="48" customHeight="1">
+          <t>Between 1.0 and 5.0. Outside this range would mean corrupted data</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>Rating is optional, only check when the field is actually there</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="50" customHeight="1">
       <c r="A58" s="32" t="n">
         <v>49</v>
       </c>
@@ -3225,39 +2839,34 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D58" s="32" t="inlineStr">
-        <is>
-          <t>Sorting</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E58" s="34" t="inlineStr">
+        <is>
+          <t>Nearby search results come back with the highest rated place first</t>
+        </is>
+      </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>Nearby search ordered by rating descending</t>
+          <t>POST to /places:searchNearby around coordinates 25.0671 and 34.8923 with rankPreference set to POPULARITY</t>
         </is>
       </c>
       <c r="G58" s="34" t="inlineStr">
         <is>
-          <t>POST to /places:searchNearby around coords 25.0671, 34.8923 with rankPreference=POPULARITY</t>
-        </is>
-      </c>
-      <c r="H58" s="34" t="inlineStr">
-        <is>
-          <t>First result rating &gt;= second result rating</t>
-        </is>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J58" s="34" t="inlineStr"/>
-    </row>
-    <row r="59" ht="48" customHeight="1">
+          <t>First result rating is equal to or higher than the second result rating</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I58" s="34" t="inlineStr"/>
+    </row>
+    <row r="59" ht="50" customHeight="1">
       <c r="A59" s="10" t="n">
         <v>50</v>
       </c>
@@ -3271,39 +2880,34 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>The text search endpoint responds within 4 seconds</t>
+        </is>
+      </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Response time under 4 seconds</t>
+          <t>Time the full request and response cycle</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Time the textsearch request</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="inlineStr">
-        <is>
-          <t>Under 4 seconds. Google APIs are generally fast, 4s gives some breathing room</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J59" s="12" t="inlineStr"/>
-    </row>
-    <row r="60" ht="48" customHeight="1">
+          <t>Under 4 seconds. Google APIs are generally fast</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60" ht="50" customHeight="1">
       <c r="A60" s="32" t="n">
         <v>51</v>
       </c>
@@ -3317,39 +2921,34 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D60" s="32" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>P1 - Critical</t>
         </is>
       </c>
+      <c r="E60" s="34" t="inlineStr">
+        <is>
+          <t>Sending a wrong API key gets a 403 back</t>
+        </is>
+      </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>Invalid API key returns 403</t>
+          <t>POST the same request but with an invalid value in the X-Goog-Api-Key header</t>
         </is>
       </c>
       <c r="G60" s="34" t="inlineStr">
         <is>
-          <t>POST the same request but with a wrong value in X-Goog-Api-Key header</t>
-        </is>
-      </c>
-      <c r="H60" s="34" t="inlineStr">
-        <is>
-          <t>HTTP 403. New API returns 403 for bad keys (old one returned 200 with REQUEST_DENIED)</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J60" s="34" t="inlineStr"/>
-    </row>
-    <row r="61" ht="48" customHeight="1">
+          <t>HTTP 403. The new API returns 403 for bad keys. The old one used to return 200 with REQUEST_DENIED in the body</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I60" s="34" t="inlineStr"/>
+    </row>
+    <row r="61" ht="50" customHeight="1">
       <c r="A61" s="10" t="n">
         <v>52</v>
       </c>
@@ -3363,420 +2962,43 @@
           <t>Google Places API</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>Data Validation</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>P2 - High</t>
         </is>
       </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Each result includes at least one food-related type</t>
+        </is>
+      </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>Result types include a food-related category</t>
+          <t>Check the types array on each result</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>Check the types array on each result</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="inlineStr">
-        <is>
           <t>At least one type is food-related: restaurant, food, cafe, meal_takeaway, or bar</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="J61" s="12" t="inlineStr"/>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A49:J49"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:G23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="B1" s="35" t="inlineStr">
-        <is>
-          <t>Test Execution Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="36" t="inlineStr">
-        <is>
-          <t>Cairo to Marsa Alam – Trip Planner QA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Google Flights UI</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Google Search - Weather</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Google Search - Restaurants</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Amadeus API - Flights</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>OpenWeatherMap API</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>Google Places API</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="37" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C11" s="37">
-        <f>SUM(C5:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="37">
-        <f>SUM(D5:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="37">
-        <f>SUM(E5:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="37">
-        <f>SUM(F5:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="37">
-        <f>SUM(G5:G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Priority Breakdown</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="38" t="inlineStr">
-        <is>
-          <t>P1 - Critical</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>P2 - High</t>
-        </is>
-      </c>
-      <c r="C15" s="41" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>P3 - Medium</t>
-        </is>
-      </c>
-      <c r="C16" s="43" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Status Key</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="44" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="C19" s="45" t="inlineStr">
-        <is>
-          <t>Test has not been executed yet</t>
-        </is>
-      </c>
-      <c r="D19" s="46" t="n"/>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="47" t="n"/>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="C20" s="45" t="inlineStr">
-        <is>
-          <t>Test executed and passed</t>
-        </is>
-      </c>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="47" t="n"/>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="49" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="C21" s="45" t="inlineStr">
-        <is>
-          <t>Test executed and failed — defect needs logging</t>
-        </is>
-      </c>
-      <c r="D21" s="46" t="n"/>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="47" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="50" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="C22" s="45" t="inlineStr">
-        <is>
-          <t>Cannot run — depends on something not ready</t>
-        </is>
-      </c>
-      <c r="D22" s="46" t="n"/>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="47" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="C23" s="45" t="inlineStr">
-        <is>
-          <t>Currently being executed</t>
-        </is>
-      </c>
-      <c r="D23" s="46" t="n"/>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="47" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A38:I38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
